--- a/satisfaction_surveys/010_skincare_tone_evenness_awareness_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/010_skincare_tone_evenness_awareness_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1245,17 +1245,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>current_tone_concerns_choices</t>
+          <t>skincare_routine_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>very_fair</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Very Fair</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>skincare_routine_choices</t>
+          <t>skincare_products_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>moisturizer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Moisturizer</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>moisturizer</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Moisturizer</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>serum</t>
+          <t>mask</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Mask</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mask</t>
+          <t>exfoliator</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mask</t>
+          <t>Exfoliator</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>exfoliator</t>
+          <t>sunscreen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Exfoliator</t>
+          <t>Sunscreen</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>skincare_products_choices</t>
+          <t>skincare_frequency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sunscreen</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sunscreen</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>several_times_a_week</t>
+          <t>several_times_a_month</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Several times a week</t>
+          <t>Several times a month</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>several_times_a_month</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Several times a month</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>skincare_frequency_choices</t>
+          <t>awareness_aware_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>strongly_agree</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Strongly Agree</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>somewhat_agree</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Somewhat Agree</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>somewhat_disagree</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Somewhat Disagree</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>awareness_aware_choices</t>
+          <t>concerns_concerns_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>strongly_disagree</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Strongly Disagree</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>hyper-pigmentation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Hyper-pigmentation</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hyper-pigmentation</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hyper-pigmentation</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>aging</t>
+          <t>dark_circles</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Dark Circles</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dark_circles</t>
+          <t>pores</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dark Circles</t>
+          <t>Pores</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>pores</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pores</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>concerns_concerns_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Word of Mouth</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>education_sources_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>word_of_mouth</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Word of Mouth</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1845,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>education_sources_choices</t>
+          <t>products_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>moisturizer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Moisturizer</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>moisturizer</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Moisturizer</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>serum</t>
+          <t>mask</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Mask</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>mask</t>
+          <t>exfoliator</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mask</t>
+          <t>Exfoliator</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>exfoliator</t>
+          <t>sunscreen</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Exfoliator</t>
+          <t>Sunscreen</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>products_choices</t>
+          <t>routine_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>sunscreen</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sunscreen</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1981,29 +1981,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>routine_choices</t>
+          <t>products_importance_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>very_important</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Very Important</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>somewhat_important</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Somewhat Important</t>
+          <t>Not Very Important</t>
         </is>
       </c>
     </row>
@@ -2049,27 +2049,10 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>not_very_important</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
-        <is>
-          <t>Not Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>products_importance_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>not_at_all_important</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
         <is>
           <t>Not At All Important</t>
         </is>
